--- a/docs/qa/sample-report.xlsx
+++ b/docs/qa/sample-report.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
-    <t>Gulf Origin International</t>
+    <t>Mcube Exporters</t>
   </si>
   <si>
     <t>Collection report · Asia/Riyadh · SAR</t>
